--- a/excel data/Catch (tonnes) - Toothfish - TOP - All Areas.xlsx
+++ b/excel data/Catch (tonnes) - Toothfish - TOP - All Areas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitytasmania-my.sharepoint.com/personal/kieran_murphy_utas_edu_au/Documents/Documents/R Projects/Prydz_Bay_mizer/excel data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqkmur13_uq_edu_au/Documents/Documents/GitHub/Prydz_Bay_mizer/excel data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:40009_{38705301-1E5A-4B3D-9504-FA76151CDAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4810F1E7-250A-4CF7-90B9-840B75D2C18F}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:40009_{38705301-1E5A-4B3D-9504-FA76151CDAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF319465-7406-4EBC-9916-678FA0306E61}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="13860" yWindow="3300" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catch (tonnes) - Toothfish - TO" sheetId="1" r:id="rId1"/>
@@ -705,9 +705,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -745,7 +745,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -851,7 +851,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -993,7 +993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1003,18 +1003,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J235"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1977</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>3.9704294499856296E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1978</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>1.6973190437587972E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1979</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>2.8710475903282542E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1980</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>8.3837753326389788E-6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1981</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>2.0405792790762799E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1982</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>2.7998645922209422E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1983</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>1.7242103985993371E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1984</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>2.1196714991955156E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1985</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>4.1918876663194899E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1986</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>5.7974597347399732E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1987</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>1.5454619811298647E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1988</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>6.9284784824450433E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1989</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>5.5839107404180371E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1990</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>5.3664071350901393E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1991</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>1.388859385293778E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1992</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>3.0363503303774568E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1993</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>2.3964942696128405E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>1994</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>5.2042680838457058E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1995</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>2.6661987402194336E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>1996</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>2.8489017686948682E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>1997</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>3.0149954309452632E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>1998</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>2.5317419660167331E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>1999</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>2.8686748237246771E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>2000</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>3.9071556738902414E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>2001</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>3.2008621482254671E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>2002</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>4.5414752792465111E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>2003</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>5.9540623305760602E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>2004</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>3.562313594170374E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>2005</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>2.4597680457082291E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>2006</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>2.8892388009556783E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>2007</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>2.9034754005771409E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>2008</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>3.1431248275384251E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>2009</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>2.7468728047410544E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>2010</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>2.0769617003311283E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>2011</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>1.4505513169867819E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>2012</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1.4766517496261298E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>2013</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>1.723419476398145E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>2014</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>1.7661292752625321E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>2015</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>1.7732475750732634E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>2016</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1.7803658748839947E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>2017</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>1.7653383530613398E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>2018</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>1.5628622695560966E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>2019</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>1.6996918103623742E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>2020</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>1.5082886376738239E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>2021</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>1.4505513169867819E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>1981</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>1982</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>1985</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>1986</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>1987</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>1988</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>1989</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>1990</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1991</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>1998</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>7.9092220119235658E-8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>1999</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>2000</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>2001</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>2002</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>2003</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>2004</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>2005</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>1.5818444023847132E-7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>2006</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>4.9828098675118462E-6</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>2007</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>2.6891354840540121E-6</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>2008</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>8.7001442131159223E-7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>2009</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>2.5625879318632352E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>2010</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>3.1478703607455793E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>2011</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>2.9580490324594133E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>2012</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>3.1557795827575026E-5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>2013</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>2.965958254471337E-5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>2014</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>3.1478703607455793E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>2015</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>1.9535778369451208E-5</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>2016</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>2.6258617079586236E-5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>2017</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>4.255161442414878E-5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>2018</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>4.8878992033687634E-5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>2019</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>3.8359726757829294E-5</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>2020</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>3.1004150286740379E-5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>2021</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>3.2269625808648147E-5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>1977</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>1.6283982897546902E-6</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>1978</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>4.9084577019748524E-5</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>1979</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>2.4813688224833376E-6</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>1980</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>1.101107414976981E-5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>1981</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>9.5377614114203285E-6</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>1982</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>1.0700903046959392E-5</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>1983</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>1.2717015215227104E-5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>1984</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>3.6739767127893917E-4</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>1985</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>1.9036751434989356E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>1986</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>1.9168574153683783E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>1987</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>1.4105030900303723E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>1988</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>7.1106725319288144E-5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>1989</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>1.0452766164711059E-4</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>1990</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>9.6928469628255369E-5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>1991</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>2.3549740980880924E-4</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>1992</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>6.0157685390080417E-4</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>1993</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>2.7892136420226764E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>1994</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>4.2160007149505955E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>1995</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>4.4284679203757316E-4</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>1996</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>4.3850439659822728E-4</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>1997</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>6.7035729594901411E-4</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>1998</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>7.8853248611978309E-4</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>1999</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>7.5449120758633987E-4</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>2000</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>9.2834211071157865E-4</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>2001</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>7.0540663056659135E-4</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>2002</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>6.3840967235954114E-4</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>2003</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>6.9206927314574335E-4</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>2004</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>6.8059294234175795E-4</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>2005</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>6.7431197750984697E-4</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>2006</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>6.778014024164642E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>2007</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>6.4701692046253024E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>2008</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>6.3623847463986822E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>2009</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>6.7276112199579489E-4</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>2010</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>6.5802799461230012E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>2011</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>6.7214077979017405E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>2012</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>6.6779838435082823E-4</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>2013</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>7.0455366003386265E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>2014</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>7.3898265244581895E-4</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>2015</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>7.6115988629676381E-4</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>2016</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>7.4859795663294185E-4</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>2017</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>7.5232000986666684E-4</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>2018</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>7.3223643095969234E-4</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>2019</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>7.5790308971725444E-4</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>2020</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>7.2238849844546158E-4</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>2021</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>7.1587490528644284E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>1981</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>1982</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>1985</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>1986</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>1987</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>1988</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>1989</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>1990</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>7.75427757026043E-8</v>
       </c>
     </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>1991</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>1998</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>1999</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>2000</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>2001</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>2002</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>2003</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>9.0725047572047026E-6</v>
       </c>
     </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>2004</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>2.0161121682677117E-6</v>
       </c>
     </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>2005</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>7.0563925889369916E-5</v>
       </c>
     </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>2006</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>6.994358368374907E-5</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>2007</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>6.521347436589021E-5</v>
       </c>
     </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>2008</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>5.6373597935793323E-5</v>
       </c>
     </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>2009</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>2.923362643988182E-5</v>
       </c>
     </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>2010</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>2.3185289935078684E-5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>2011</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>2.7760313701532339E-5</v>
       </c>
     </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>2012</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>1.6671696776059925E-5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>2013</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>4.0322243365354234E-6</v>
       </c>
     </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>2014</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>7.8318203459630347E-6</v>
       </c>
     </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>2015</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>1.0313189168446372E-5</v>
       </c>
     </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>2016</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>3.1249738608149535E-5</v>
       </c>
     </row>
-    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>2017</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>1.8920437271435449E-5</v>
       </c>
     </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>2018</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>2.3883174916402124E-5</v>
       </c>
     </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>2019</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>4.0322243365354234E-6</v>
       </c>
     </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>2020</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>4.4974809907510493E-6</v>
       </c>
     </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>2021</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>4.7301093178588622E-6</v>
       </c>
     </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>1977</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>1978</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>1979</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>1980</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>1981</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>1982</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>1983</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>1984</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>1985</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>1986</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>1987</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>1988</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>1989</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>1990</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>1991</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>1992</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>1993</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>1994</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>1995</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>1996</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>1997</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>1998</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>9.6295426356281605E-8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>1999</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>9.6295426356281605E-8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>2000</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>2001</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>3.2740444961135748E-6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>2002</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>1.1555451162753793E-6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>2003</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>2.503681085263322E-6</v>
       </c>
     </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>2004</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>1.251840542631661E-6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>2005</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>6.7406798449397124E-7</v>
       </c>
     </row>
-    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>2006</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>9.6295426356281605E-8</v>
       </c>
     </row>
-    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>2007</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>1.1555451162753793E-6</v>
       </c>
     </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>2008</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>8.6665883720653445E-7</v>
       </c>
     </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>2009</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>1.6370222480567874E-6</v>
       </c>
     </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>2010</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>2011</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>2.8888627906884482E-7</v>
       </c>
     </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>2012</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>4.8147713178140803E-7</v>
       </c>
     </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>2013</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>2014</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>3.8518170542512642E-7</v>
       </c>
     </row>
-    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>2015</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>9.6295426356281605E-8</v>
       </c>
     </row>
-    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>2016</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>4.8147713178140803E-7</v>
       </c>
     </row>
-    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>2017</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>9.6295426356281605E-8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>2018</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>2019</v>
       </c>
@@ -5416,7 +5416,7 @@
         <v>1.9259085271256321E-7</v>
       </c>
     </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>2020</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>2021</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>9.6295426356281605E-7</v>
       </c>
     </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>1981</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>1982</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>1985</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>1986</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>1987</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>1988</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>1989</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>1990</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>1991</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>1998</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>3.9481124806075461E-6</v>
       </c>
     </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>1999</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>2.8503446201459354E-5</v>
       </c>
     </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>2000</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>7.2317865193567484E-5</v>
       </c>
     </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>2001</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>6.0280936899032286E-5</v>
       </c>
     </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>2002</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>1.303840072864053E-4</v>
       </c>
     </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>2003</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>1.8402055976685414E-4</v>
       </c>
     </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>2004</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>2.4632370061936835E-4</v>
       </c>
     </row>
-    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>2005</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>3.3809324193690473E-4</v>
       </c>
     </row>
-    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>2006</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>3.3530067457257257E-4</v>
       </c>
     </row>
-    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>2007</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>3.299081306966208E-4</v>
       </c>
     </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>2008</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>2.5681990209220306E-4</v>
       </c>
     </row>
-    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>2009</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>2.8079746325491718E-4</v>
       </c>
     </row>
-    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>2010</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>3.0641204666568807E-4</v>
       </c>
     </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>2011</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>3.3038960782840219E-4</v>
       </c>
     </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>2012</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>3.4675983030897005E-4</v>
       </c>
     </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>2013</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>3.5032276108415249E-4</v>
       </c>
     </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>2014</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>3.2230079201447454E-4</v>
       </c>
     </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>2015</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>3.3289328891366552E-4</v>
       </c>
     </row>
-    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>2016</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>3.2750074503771375E-4</v>
       </c>
     </row>
-    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>2017</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>3.4310060410743139E-4</v>
       </c>
     </row>
-    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>2018</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>3.3453031116172229E-4</v>
       </c>
     </row>
-    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>2019</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>3.7189293658795956E-4</v>
       </c>
     </row>
-    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>2020</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>3.5725603178180475E-4</v>
       </c>
     </row>
-    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>2021</v>
       </c>
@@ -6190,7 +6190,12 @@
   <autoFilter ref="A1:F235" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
+        <filter val="2005"/>
+        <filter val="2006"/>
         <filter val="2007"/>
+        <filter val="2008"/>
+        <filter val="2009"/>
+        <filter val="2010"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -6208,30 +6213,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.7265625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.81640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="1"/>
+    <col min="18" max="18" width="9.1796875" style="1"/>
     <col min="19" max="19" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -6284,7 +6289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>2005</v>
       </c>
@@ -6334,7 +6339,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2006</v>
       </c>
@@ -6380,11 +6385,11 @@
         <v>3.2326842759183012E-6</v>
       </c>
       <c r="Q3" s="1">
-        <f t="shared" ref="Q3:Q58" si="2">K3/C3</f>
+        <f t="shared" ref="Q3:Q48" si="2">K3/C3</f>
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2007</v>
       </c>
@@ -6441,7 +6446,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2008</v>
       </c>
@@ -6491,7 +6496,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2009</v>
       </c>
@@ -6548,7 +6553,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2010</v>
       </c>
@@ -6605,7 +6610,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>2011</v>
       </c>
@@ -6662,7 +6667,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>2012</v>
       </c>
@@ -6712,7 +6717,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -6762,7 +6767,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>2014</v>
       </c>
@@ -6812,7 +6817,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>2015</v>
       </c>
@@ -6862,7 +6867,7 @@
         <v>2.1551228506122008E-7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>2016</v>
       </c>
@@ -6912,7 +6917,7 @@
         <v>4.3102457012244016E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>2017</v>
       </c>
@@ -6962,7 +6967,7 @@
         <v>4.3102457012244016E-7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>2018</v>
       </c>
@@ -7012,7 +7017,7 @@
         <v>4.3102457012244016E-7</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>2019</v>
       </c>
@@ -7059,7 +7064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>2020</v>
       </c>
@@ -7106,7 +7111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>2021</v>
       </c>
@@ -7153,7 +7158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>2022</v>
       </c>
@@ -7200,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>2003</v>
       </c>
@@ -7250,7 +7255,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>2004</v>
       </c>
@@ -7300,7 +7305,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>2005</v>
       </c>
@@ -7350,7 +7355,7 @@
         <v>1.2617800017547573E-6</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>2006</v>
       </c>
@@ -7400,7 +7405,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>2007</v>
       </c>
@@ -7450,7 +7455,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>2008</v>
       </c>
@@ -7500,7 +7505,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>2009</v>
       </c>
@@ -7557,7 +7562,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>2010</v>
       </c>
@@ -7613,7 +7618,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>2011</v>
       </c>
@@ -7669,7 +7674,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>2012</v>
       </c>
@@ -7719,7 +7724,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>2013</v>
       </c>
@@ -7769,7 +7774,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>2014</v>
       </c>
@@ -7816,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>2015</v>
       </c>
@@ -7866,7 +7871,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>2016</v>
       </c>
@@ -7913,7 +7918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>2017</v>
       </c>
@@ -7963,7 +7968,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>2018</v>
       </c>
@@ -8013,7 +8018,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>2019</v>
       </c>
@@ -8063,7 +8068,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>2020</v>
       </c>
@@ -8113,7 +8118,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>2021</v>
       </c>
@@ -8163,7 +8168,7 @@
         <v>6.3089000087737865E-7</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>2022</v>
       </c>
@@ -8213,7 +8218,7 @@
         <v>1.892670002632136E-6</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>2004</v>
       </c>
@@ -8263,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>2005</v>
       </c>
@@ -8313,7 +8318,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>2006</v>
       </c>
@@ -8363,7 +8368,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>2007</v>
       </c>
@@ -8421,7 +8426,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>2008</v>
       </c>
@@ -8471,7 +8476,7 @@
         <v>2.9416071564830875E-6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>2009</v>
       </c>
@@ -8521,7 +8526,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>2010</v>
       </c>
@@ -8571,7 +8576,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>2011</v>
       </c>
@@ -8621,7 +8626,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>2012</v>
       </c>
@@ -8671,7 +8676,7 @@
         <v>1.4708035782415438E-6</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>2013</v>
       </c>
@@ -8718,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>2014</v>
       </c>
@@ -8765,7 +8770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>2015</v>
       </c>
@@ -8812,7 +8817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>2016</v>
       </c>
@@ -8859,7 +8864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>2017</v>
       </c>
@@ -8906,7 +8911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>2018</v>
       </c>
@@ -8953,7 +8958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>2019</v>
       </c>
@@ -9000,7 +9005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>2020</v>
       </c>
@@ -9047,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>2021</v>
       </c>
@@ -9094,7 +9099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>2022</v>
       </c>
@@ -9141,7 +9146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
         <v>25</v>
       </c>
@@ -9158,7 +9163,7 @@
         <v>2.3510431097587642E-7</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
         <v>14</v>
       </c>
@@ -9175,7 +9180,7 @@
         <v>5.1618272799058253E-7</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
         <v>24</v>
       </c>
@@ -9192,7 +9197,7 @@
         <v>4.0112824861133014E-7</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C69" s="1">
         <f>SUM(C65:C67)/3</f>
         <v>4.3676824984178844E-5</v>
